--- a/Simulation_studies/lhc_parameter_comparison_Xdim1_playaround.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim1_playaround.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\OneDrive\KU, MAT-OEK\Kandidat\Thesis\Thesis_linear_CDS\Simulation_studies\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ec18ff9d9d96f3/KU^J MAT-OEK/Kandidat/Thesis/Thesis_linear_CDS/Simulation_studies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CA9755-158A-4331-91C2-E162CCF5A3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DF3ADE80-0726-45E1-B892-B7A5BB7A274C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E91F3C8D-C4C2-4416-BD23-48DC9044F402}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$O$17</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$O$18</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="35">
   <si>
     <t>Parameter</t>
   </si>
@@ -132,14 +132,31 @@
   </si>
   <si>
     <t>d=3</t>
+  </si>
+  <si>
+    <t>LHS</t>
+  </si>
+  <si>
+    <t>RHS</t>
+  </si>
+  <si>
+    <t>bound/kappas</t>
+  </si>
+  <si>
+    <t>kappas-bound</t>
+  </si>
+  <si>
+    <t>bar/kappas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.00000000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.00000000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -191,13 +208,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" width="12.26953125" customWidth="1"/>
@@ -508,7 +527,7 @@
     <col min="13" max="13" width="14.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -560,7 +579,7 @@
         <v>1.2982885089934081E-9</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -601,7 +620,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -627,7 +646,7 @@
         <v>51.329834605162247</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -653,7 +672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -683,7 +702,7 @@
         <v>1.7424390942318398E-4</v>
       </c>
       <c r="L6" s="2">
-        <f t="shared" ref="K6:L6" si="0">(0.0005-0.0005/C2)</f>
+        <f t="shared" ref="L6" si="0">(0.0005-0.0005/C2)</f>
         <v>1.6619252994987333E-4</v>
       </c>
       <c r="M6" s="2">
@@ -691,7 +710,7 @@
         <v>1.6619252995420721E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -717,7 +736,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -743,7 +762,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -769,7 +788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -798,7 +817,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -831,7 +850,7 @@
         <v>1.5341232733825272</v>
       </c>
       <c r="L11">
-        <f t="shared" ref="L11:M11" si="1">(1-0.0005)*C2</f>
+        <f t="shared" ref="L11" si="1">(1-0.0005)*C2</f>
         <v>1.4971204806320073</v>
       </c>
       <c r="M11">
@@ -839,7 +858,7 @@
         <v>1.4971204806514447</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -865,7 +884,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -891,7 +910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="J16" t="s">
         <v>23</v>
       </c>
@@ -901,8 +920,14 @@
       <c r="L16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="O16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J17" t="s">
         <v>13</v>
       </c>
@@ -912,8 +937,22 @@
       <c r="L17">
         <v>0.20100000000000001</v>
       </c>
-    </row>
-    <row r="18" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="M17" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17">
+        <f>L18*L19*L20*L17</f>
+        <v>5.6480317001999986E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="3">
+        <f>J11/(B2-B8)</f>
+        <v>3.0478727301253065E-4</v>
+      </c>
       <c r="J18" t="s">
         <v>11</v>
       </c>
@@ -923,8 +962,27 @@
       <c r="L18">
         <v>0.84099999999999997</v>
       </c>
-    </row>
-    <row r="19" spans="10:12" x14ac:dyDescent="0.35">
+      <c r="M18" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="5">
+        <f>$J$11*(1-J11/L21)*(1-J11/L22)*(1-J11/L23)</f>
+        <v>4.9877934751929348E-4</v>
+      </c>
+      <c r="O18" s="4">
+        <f>J11/(L21*L22*L23)</f>
+        <v>1.5393219483850575E-3</v>
+      </c>
+      <c r="P18" s="3">
+        <f>(L21-J11)*(L22-J11)*(L23-J11)</f>
+        <v>0.32402535937500004</v>
+      </c>
+      <c r="Q18" s="3">
+        <f>O18*P18</f>
+        <v>4.9877934751929348E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J19" t="s">
         <v>24</v>
       </c>
@@ -935,7 +993,7 @@
         <v>0.69899999999999995</v>
       </c>
     </row>
-    <row r="20" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J20" t="s">
         <v>25</v>
       </c>
@@ -943,7 +1001,7 @@
         <v>0.47799999999999998</v>
       </c>
     </row>
-    <row r="21" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J21" t="s">
         <v>8</v>
       </c>
@@ -955,7 +1013,7 @@
         <v>1.2629999999999999</v>
       </c>
     </row>
-    <row r="22" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J22" t="s">
         <v>26</v>
       </c>
@@ -966,7 +1024,7 @@
         <v>0.66800000000000004</v>
       </c>
     </row>
-    <row r="23" spans="10:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
       <c r="J23" t="s">
         <v>27</v>
       </c>
